--- a/artfynd/A 18387-2025 artfynd.xlsx
+++ b/artfynd/A 18387-2025 artfynd.xlsx
@@ -821,7 +821,7 @@
         <v>125028585</v>
       </c>
       <c r="B3" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18387-2025 artfynd.xlsx
+++ b/artfynd/A 18387-2025 artfynd.xlsx
@@ -821,7 +821,7 @@
         <v>125028585</v>
       </c>
       <c r="B3" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
